--- a/results/multi_city/inj/inj_data.xlsx
+++ b/results/multi_city/inj/inj_data.xlsx
@@ -27803,7 +27803,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:I105"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -27844,6 +27844,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>mode_distance</t>
         </is>
       </c>
@@ -27883,6 +27888,9 @@
         </is>
       </c>
       <c r="H2">
+        <v>7.347686590275595</v>
+      </c>
+      <c r="I2">
         <v>38891386.71347463</v>
       </c>
     </row>
@@ -27921,6 +27929,9 @@
         </is>
       </c>
       <c r="H3">
+        <v>20.70711675441322</v>
+      </c>
+      <c r="I3">
         <v>28185306.86771144</v>
       </c>
     </row>
@@ -27959,6 +27970,9 @@
         </is>
       </c>
       <c r="H4">
+        <v>63.01197894084871</v>
+      </c>
+      <c r="I4">
         <v>3028905.406826921</v>
       </c>
     </row>
@@ -27997,6 +28011,9 @@
         </is>
       </c>
       <c r="H5">
+        <v>195.2703375658098</v>
+      </c>
+      <c r="I5">
         <v>14050058.88347711</v>
       </c>
     </row>
@@ -28035,6 +28052,9 @@
         </is>
       </c>
       <c r="H6">
+        <v>166.9928770517168</v>
+      </c>
+      <c r="I6">
         <v>7623586.646322806</v>
       </c>
     </row>
@@ -28073,6 +28093,9 @@
         </is>
       </c>
       <c r="H7">
+        <v>1.558600188894429</v>
+      </c>
+      <c r="I7">
         <v>6761083.388006915</v>
       </c>
     </row>
@@ -28111,6 +28134,9 @@
         </is>
       </c>
       <c r="H8">
+        <v>230.0048559925655</v>
+      </c>
+      <c r="I8">
         <v>10652492.05314973</v>
       </c>
     </row>
@@ -28149,7 +28175,10 @@
         </is>
       </c>
       <c r="H9">
-        <v>130230378.3012547</v>
+        <v>454.8885970919586</v>
+      </c>
+      <c r="I9">
+        <v>124450572.1777957</v>
       </c>
     </row>
     <row r="10">
@@ -28187,6 +28216,9 @@
         </is>
       </c>
       <c r="H10">
+        <v>13.33638695841394</v>
+      </c>
+      <c r="I10">
         <v>38891386.71347463</v>
       </c>
     </row>
@@ -28225,6 +28257,9 @@
         </is>
       </c>
       <c r="H11">
+        <v>33.12651834974945</v>
+      </c>
+      <c r="I11">
         <v>28185306.86771144</v>
       </c>
     </row>
@@ -28263,6 +28298,9 @@
         </is>
       </c>
       <c r="H12">
+        <v>81.2177953946539</v>
+      </c>
+      <c r="I12">
         <v>3028905.406826921</v>
       </c>
     </row>
@@ -28301,6 +28339,9 @@
         </is>
       </c>
       <c r="H13">
+        <v>245.2819588808486</v>
+      </c>
+      <c r="I13">
         <v>14050058.88347711</v>
       </c>
     </row>
@@ -28339,6 +28380,9 @@
         </is>
       </c>
       <c r="H14">
+        <v>206.4283481520472</v>
+      </c>
+      <c r="I14">
         <v>7623586.646322806</v>
       </c>
     </row>
@@ -28377,6 +28421,9 @@
         </is>
       </c>
       <c r="H15">
+        <v>4.757373585393693</v>
+      </c>
+      <c r="I15">
         <v>6761083.388006915</v>
       </c>
     </row>
@@ -28415,6 +28462,9 @@
         </is>
       </c>
       <c r="H16">
+        <v>287.6461435467011</v>
+      </c>
+      <c r="I16">
         <v>10652492.05314973</v>
       </c>
     </row>
@@ -28453,7 +28503,10 @@
         </is>
       </c>
       <c r="H17">
-        <v>130230378.3012547</v>
+        <v>584.1483813211067</v>
+      </c>
+      <c r="I17">
+        <v>124450572.1777957</v>
       </c>
     </row>
     <row r="18">
@@ -28491,6 +28544,9 @@
         </is>
       </c>
       <c r="H18">
+        <v>4.13192386434712</v>
+      </c>
+      <c r="I18">
         <v>38891386.71347463</v>
       </c>
     </row>
@@ -28529,6 +28585,9 @@
         </is>
       </c>
       <c r="H19">
+        <v>13.13399197567636</v>
+      </c>
+      <c r="I19">
         <v>28185306.86771144</v>
       </c>
     </row>
@@ -28567,6 +28626,9 @@
         </is>
       </c>
       <c r="H20">
+        <v>49.29447139884455</v>
+      </c>
+      <c r="I20">
         <v>3028905.406826921</v>
       </c>
     </row>
@@ -28605,6 +28667,9 @@
         </is>
       </c>
       <c r="H21">
+        <v>156.8638600821543</v>
+      </c>
+      <c r="I21">
         <v>14050058.88347711</v>
       </c>
     </row>
@@ -28643,6 +28708,9 @@
         </is>
       </c>
       <c r="H22">
+        <v>135.3218552793651</v>
+      </c>
+      <c r="I22">
         <v>7623586.646322806</v>
       </c>
     </row>
@@ -28681,6 +28749,9 @@
         </is>
       </c>
       <c r="H23">
+        <v>0.5351892783569997</v>
+      </c>
+      <c r="I23">
         <v>6761083.388006915</v>
       </c>
     </row>
@@ -28719,6 +28790,9 @@
         </is>
       </c>
       <c r="H24">
+        <v>184.6163266782096</v>
+      </c>
+      <c r="I24">
         <v>10652492.05314973</v>
       </c>
     </row>
@@ -28757,7 +28831,10 @@
         </is>
       </c>
       <c r="H25">
-        <v>130230378.3012547</v>
+        <v>359.2812918787445</v>
+      </c>
+      <c r="I25">
+        <v>124450572.1777957</v>
       </c>
     </row>
     <row r="26">
@@ -28795,6 +28872,9 @@
         </is>
       </c>
       <c r="H26">
+        <v>8.123737566786236</v>
+      </c>
+      <c r="I26">
         <v>45017466.82029755</v>
       </c>
     </row>
@@ -28833,6 +28913,9 @@
         </is>
       </c>
       <c r="H27">
+        <v>18.84825698072325</v>
+      </c>
+      <c r="I27">
         <v>23071166.16419978</v>
       </c>
     </row>
@@ -28871,6 +28954,9 @@
         </is>
       </c>
       <c r="H28">
+        <v>57.20989242906023</v>
+      </c>
+      <c r="I28">
         <v>2575065.755478045</v>
       </c>
     </row>
@@ -28909,6 +28995,9 @@
         </is>
       </c>
       <c r="H29">
+        <v>181.8480682764644</v>
+      </c>
+      <c r="I29">
         <v>12538604.24289905</v>
       </c>
     </row>
@@ -28947,6 +29036,9 @@
         </is>
       </c>
       <c r="H30">
+        <v>166.9430019755086</v>
+      </c>
+      <c r="I30">
         <v>7716790.160518484</v>
       </c>
     </row>
@@ -28985,6 +29077,9 @@
         </is>
       </c>
       <c r="H31">
+        <v>1.549881374089115</v>
+      </c>
+      <c r="I31">
         <v>6761083.388006915</v>
       </c>
     </row>
@@ -29023,6 +29118,9 @@
         </is>
       </c>
       <c r="H32">
+        <v>224.1528944045688</v>
+      </c>
+      <c r="I32">
         <v>10291855.91599653</v>
       </c>
     </row>
@@ -29061,7 +29159,10 @@
         </is>
       </c>
       <c r="H33">
-        <v>125316843.1560066</v>
+        <v>434.5228386026318</v>
+      </c>
+      <c r="I33">
+        <v>120585765.7866152</v>
       </c>
     </row>
     <row r="34">
@@ -29099,6 +29200,9 @@
         </is>
       </c>
       <c r="H34">
+        <v>14.71276422392734</v>
+      </c>
+      <c r="I34">
         <v>45017466.82029755</v>
       </c>
     </row>
@@ -29137,6 +29241,9 @@
         </is>
       </c>
       <c r="H35">
+        <v>30.12487924264239</v>
+      </c>
+      <c r="I35">
         <v>23071166.16419978</v>
       </c>
     </row>
@@ -29175,6 +29282,9 @@
         </is>
       </c>
       <c r="H36">
+        <v>73.65758489049199</v>
+      </c>
+      <c r="I36">
         <v>2575065.755478045</v>
       </c>
     </row>
@@ -29213,6 +29323,9 @@
         </is>
       </c>
       <c r="H37">
+        <v>228.3452510049133</v>
+      </c>
+      <c r="I37">
         <v>12538604.24289905</v>
       </c>
     </row>
@@ -29251,6 +29364,9 @@
         </is>
       </c>
       <c r="H38">
+        <v>206.2774829054267</v>
+      </c>
+      <c r="I38">
         <v>7716790.160518484</v>
       </c>
     </row>
@@ -29289,6 +29405,9 @@
         </is>
       </c>
       <c r="H39">
+        <v>4.720955231641188</v>
+      </c>
+      <c r="I39">
         <v>6761083.388006915</v>
       </c>
     </row>
@@ -29327,6 +29446,9 @@
         </is>
       </c>
       <c r="H40">
+        <v>279.9350677959187</v>
+      </c>
+      <c r="I40">
         <v>10291855.91599653</v>
       </c>
     </row>
@@ -29365,7 +29487,10 @@
         </is>
       </c>
       <c r="H41">
-        <v>125316843.1560066</v>
+        <v>557.838917499043</v>
+      </c>
+      <c r="I41">
+        <v>120585765.7866152</v>
       </c>
     </row>
     <row r="42">
@@ -29403,6 +29528,9 @@
         </is>
       </c>
       <c r="H42">
+        <v>4.576996659360509</v>
+      </c>
+      <c r="I42">
         <v>45017466.82029755</v>
       </c>
     </row>
@@ -29441,6 +29569,9 @@
         </is>
       </c>
       <c r="H43">
+        <v>11.9639747572446</v>
+      </c>
+      <c r="I43">
         <v>23071166.16419978</v>
       </c>
     </row>
@@ -29479,6 +29610,9 @@
         </is>
       </c>
       <c r="H44">
+        <v>44.79097930624523</v>
+      </c>
+      <c r="I44">
         <v>2575065.755478045</v>
       </c>
     </row>
@@ -29517,6 +29651,9 @@
         </is>
       </c>
       <c r="H45">
+        <v>146.1196537233451</v>
+      </c>
+      <c r="I45">
         <v>12538604.24289905</v>
       </c>
     </row>
@@ -29555,6 +29692,9 @@
         </is>
       </c>
       <c r="H46">
+        <v>135.3324927584953</v>
+      </c>
+      <c r="I46">
         <v>7716790.160518484</v>
       </c>
     </row>
@@ -29593,6 +29733,9 @@
         </is>
       </c>
       <c r="H47">
+        <v>0.5331013715075518</v>
+      </c>
+      <c r="I47">
         <v>6761083.388006915</v>
       </c>
     </row>
@@ -29631,6 +29774,9 @@
         </is>
       </c>
       <c r="H48">
+        <v>180.1234720647405</v>
+      </c>
+      <c r="I48">
         <v>10291855.91599653</v>
       </c>
     </row>
@@ -29669,7 +29815,10 @@
         </is>
       </c>
       <c r="H49">
-        <v>125316843.1560066</v>
+        <v>343.3171985761982</v>
+      </c>
+      <c r="I49">
+        <v>120585765.7866152</v>
       </c>
     </row>
     <row r="50">
@@ -29707,6 +29856,9 @@
         </is>
       </c>
       <c r="H50">
+        <v>6.779787111687368</v>
+      </c>
+      <c r="I50">
         <v>34632280.38944122</v>
       </c>
     </row>
@@ -29745,6 +29897,9 @@
         </is>
       </c>
       <c r="H51">
+        <v>23.16051569415969</v>
+      </c>
+      <c r="I51">
         <v>34244711.29804936</v>
       </c>
     </row>
@@ -29783,6 +29938,9 @@
         </is>
       </c>
       <c r="H52">
+        <v>60.14520896089905</v>
+      </c>
+      <c r="I52">
         <v>2749183.185668746</v>
       </c>
     </row>
@@ -29821,6 +29979,9 @@
         </is>
       </c>
       <c r="H53">
+        <v>190.0872503389324</v>
+      </c>
+      <c r="I53">
         <v>13210804.28340078</v>
       </c>
     </row>
@@ -29859,6 +30020,9 @@
         </is>
       </c>
       <c r="H54">
+        <v>161.9152904393324</v>
+      </c>
+      <c r="I54">
         <v>7111725.767632352</v>
       </c>
     </row>
@@ -29897,6 +30061,9 @@
         </is>
       </c>
       <c r="H55">
+        <v>1.559935739396839</v>
+      </c>
+      <c r="I55">
         <v>6761083.388006915</v>
       </c>
     </row>
@@ -29935,6 +30102,9 @@
         </is>
       </c>
       <c r="H56">
+        <v>222.0604994002315</v>
+      </c>
+      <c r="I56">
         <v>9860908.953301098</v>
       </c>
     </row>
@@ -29973,7 +30143,10 @@
         </is>
       </c>
       <c r="H57">
-        <v>135156546.2246397</v>
+        <v>443.6479882844077</v>
+      </c>
+      <c r="I57">
+        <v>128134171.3047735</v>
       </c>
     </row>
     <row r="58">
@@ -30011,6 +30184,9 @@
         </is>
       </c>
       <c r="H58">
+        <v>12.32735067911349</v>
+      </c>
+      <c r="I58">
         <v>34632280.38944122</v>
       </c>
     </row>
@@ -30049,6 +30225,9 @@
         </is>
       </c>
       <c r="H59">
+        <v>36.89490570830991</v>
+      </c>
+      <c r="I59">
         <v>34244711.29804936</v>
       </c>
     </row>
@@ -30087,6 +30266,9 @@
         </is>
       </c>
       <c r="H60">
+        <v>77.44049410528518</v>
+      </c>
+      <c r="I60">
         <v>2749183.185668746</v>
       </c>
     </row>
@@ -30125,6 +30307,9 @@
         </is>
       </c>
       <c r="H61">
+        <v>238.4838890428657</v>
+      </c>
+      <c r="I61">
         <v>13210804.28340078</v>
       </c>
     </row>
@@ -30163,6 +30348,9 @@
         </is>
       </c>
       <c r="H62">
+        <v>200.1068543096153</v>
+      </c>
+      <c r="I62">
         <v>7111725.767632352</v>
       </c>
     </row>
@@ -30201,6 +30389,9 @@
         </is>
       </c>
       <c r="H63">
+        <v>4.762769065742962</v>
+      </c>
+      <c r="I63">
         <v>6761083.388006915</v>
       </c>
     </row>
@@ -30239,6 +30430,9 @@
         </is>
       </c>
       <c r="H64">
+        <v>277.5473484149005</v>
+      </c>
+      <c r="I64">
         <v>9860908.953301098</v>
       </c>
     </row>
@@ -30277,7 +30471,10 @@
         </is>
       </c>
       <c r="H65">
-        <v>135156546.2246397</v>
+        <v>570.0162629109326</v>
+      </c>
+      <c r="I65">
+        <v>128134171.3047735</v>
       </c>
     </row>
     <row r="66">
@@ -30315,6 +30512,9 @@
         </is>
       </c>
       <c r="H66">
+        <v>3.805850911804931</v>
+      </c>
+      <c r="I66">
         <v>34632280.38944122</v>
       </c>
     </row>
@@ -30353,6 +30553,9 @@
         </is>
       </c>
       <c r="H67">
+        <v>14.75052371824379</v>
+      </c>
+      <c r="I67">
         <v>34244711.29804936</v>
       </c>
     </row>
@@ -30391,6 +30594,9 @@
         </is>
       </c>
       <c r="H68">
+        <v>47.09301316299027</v>
+      </c>
+      <c r="I68">
         <v>2749183.185668746</v>
       </c>
     </row>
@@ -30429,6 +30635,9 @@
         </is>
       </c>
       <c r="H69">
+        <v>152.8648055397966</v>
+      </c>
+      <c r="I69">
         <v>13210804.28340078</v>
       </c>
     </row>
@@ -30467,6 +30676,9 @@
         </is>
       </c>
       <c r="H70">
+        <v>131.2308899632981</v>
+      </c>
+      <c r="I70">
         <v>7111725.767632352</v>
       </c>
     </row>
@@ -30505,6 +30717,9 @@
         </is>
       </c>
       <c r="H71">
+        <v>0.5355192511703383</v>
+      </c>
+      <c r="I71">
         <v>6761083.388006915</v>
       </c>
     </row>
@@ -30543,6 +30758,9 @@
         </is>
       </c>
       <c r="H72">
+        <v>178.3239031262884</v>
+      </c>
+      <c r="I72">
         <v>9860908.953301098</v>
       </c>
     </row>
@@ -30581,7 +30799,10 @@
         </is>
       </c>
       <c r="H73">
-        <v>135156546.2246397</v>
+        <v>350.2806025473041</v>
+      </c>
+      <c r="I73">
+        <v>128134171.3047735</v>
       </c>
     </row>
     <row r="74">
@@ -30619,6 +30840,9 @@
         </is>
       </c>
       <c r="H74">
+        <v>7.161186122216339</v>
+      </c>
+      <c r="I74">
         <v>37473492.28202599</v>
       </c>
     </row>
@@ -30657,6 +30881,9 @@
         </is>
       </c>
       <c r="H75">
+        <v>20.32272312306667</v>
+      </c>
+      <c r="I75">
         <v>27213914.0452881</v>
       </c>
     </row>
@@ -30695,6 +30922,9 @@
         </is>
       </c>
       <c r="H76">
+        <v>77.18559968773279</v>
+      </c>
+      <c r="I76">
         <v>6201990.383908763</v>
       </c>
     </row>
@@ -30733,6 +30963,9 @@
         </is>
       </c>
       <c r="H77">
+        <v>192.0475267925603</v>
+      </c>
+      <c r="I77">
         <v>13769665.0567956</v>
       </c>
     </row>
@@ -30771,6 +31004,9 @@
         </is>
       </c>
       <c r="H78">
+        <v>162.1830322899874</v>
+      </c>
+      <c r="I78">
         <v>7181369.296209926</v>
       </c>
     </row>
@@ -30809,6 +31045,9 @@
         </is>
       </c>
       <c r="H79">
+        <v>1.554795527238988</v>
+      </c>
+      <c r="I79">
         <v>6761083.388006915</v>
       </c>
     </row>
@@ -30847,6 +31086,9 @@
         </is>
       </c>
       <c r="H80">
+        <v>239.3686319777202</v>
+      </c>
+      <c r="I80">
         <v>13383359.68011869</v>
       </c>
     </row>
@@ -30885,7 +31127,10 @@
         </is>
       </c>
       <c r="H81">
-        <v>129395956.970525</v>
+        <v>460.4548635428025</v>
+      </c>
+      <c r="I81">
+        <v>123815349.0395738</v>
       </c>
     </row>
     <row r="82">
@@ -30923,6 +31168,9 @@
         </is>
       </c>
       <c r="H82">
+        <v>12.99765100691752</v>
+      </c>
+      <c r="I82">
         <v>37473492.28202599</v>
       </c>
     </row>
@@ -30961,6 +31209,9 @@
         </is>
       </c>
       <c r="H83">
+        <v>32.51199684021981</v>
+      </c>
+      <c r="I83">
         <v>27213914.0452881</v>
       </c>
     </row>
@@ -30999,6 +31250,9 @@
         </is>
       </c>
       <c r="H84">
+        <v>101.5398531562096</v>
+      </c>
+      <c r="I84">
         <v>6201990.383908763</v>
       </c>
     </row>
@@ -31037,6 +31291,9 @@
         </is>
       </c>
       <c r="H85">
+        <v>241.6374808696616</v>
+      </c>
+      <c r="I85">
         <v>13769665.0567956</v>
       </c>
     </row>
@@ -31075,6 +31332,9 @@
         </is>
       </c>
       <c r="H86">
+        <v>200.7530469103486</v>
+      </c>
+      <c r="I86">
         <v>7181369.296209926</v>
       </c>
     </row>
@@ -31113,6 +31373,9 @@
         </is>
       </c>
       <c r="H87">
+        <v>4.742335911402603</v>
+      </c>
+      <c r="I87">
         <v>6761083.388006915</v>
       </c>
     </row>
@@ -31151,6 +31414,9 @@
         </is>
       </c>
       <c r="H88">
+        <v>302.2929000665582</v>
+      </c>
+      <c r="I88">
         <v>13383359.68011869</v>
       </c>
     </row>
@@ -31189,7 +31455,10 @@
         </is>
       </c>
       <c r="H89">
-        <v>129395956.970525</v>
+        <v>594.1823646947597</v>
+      </c>
+      <c r="I89">
+        <v>123815349.0395738</v>
       </c>
     </row>
     <row r="90">
@@ -31227,6 +31496,9 @@
         </is>
       </c>
       <c r="H90">
+        <v>4.027156377250619</v>
+      </c>
+      <c r="I90">
         <v>37473492.28202599</v>
       </c>
     </row>
@@ -31265,6 +31537,9 @@
         </is>
       </c>
       <c r="H91">
+        <v>12.88990012024656</v>
+      </c>
+      <c r="I91">
         <v>27213914.0452881</v>
       </c>
     </row>
@@ -31303,6 +31578,9 @@
         </is>
       </c>
       <c r="H92">
+        <v>59.38781832931565</v>
+      </c>
+      <c r="I92">
         <v>6201990.383908763</v>
       </c>
     </row>
@@ -31341,6 +31619,9 @@
         </is>
       </c>
       <c r="H93">
+        <v>154.0714494538878</v>
+      </c>
+      <c r="I93">
         <v>13769665.0567956</v>
       </c>
     </row>
@@ -31379,6 +31660,9 @@
         </is>
       </c>
       <c r="H94">
+        <v>131.2952621713002</v>
+      </c>
+      <c r="I94">
         <v>7181369.296209926</v>
       </c>
     </row>
@@ -31417,6 +31701,9 @@
         </is>
       </c>
       <c r="H95">
+        <v>0.5342322380812004</v>
+      </c>
+      <c r="I95">
         <v>6761083.388006915</v>
       </c>
     </row>
@@ -31455,6 +31742,9 @@
         </is>
       </c>
       <c r="H96">
+        <v>190.6830805006159</v>
+      </c>
+      <c r="I96">
         <v>13383359.68011869</v>
       </c>
     </row>
@@ -31493,7 +31783,10 @@
         </is>
       </c>
       <c r="H97">
-        <v>129395956.970525</v>
+        <v>362.2058186900821</v>
+      </c>
+      <c r="I97">
+        <v>123815349.0395738</v>
       </c>
     </row>
     <row r="98">
@@ -31530,7 +31823,7 @@
           <t>Latin_America</t>
         </is>
       </c>
-      <c r="H98">
+      <c r="I98">
         <v>38891386.71347463</v>
       </c>
     </row>
@@ -31568,7 +31861,7 @@
           <t>Latin_America</t>
         </is>
       </c>
-      <c r="H99">
+      <c r="I99">
         <v>28185306.86771144</v>
       </c>
     </row>
@@ -31606,7 +31899,7 @@
           <t>Latin_America</t>
         </is>
       </c>
-      <c r="H100">
+      <c r="I100">
         <v>3028905.406826921</v>
       </c>
     </row>
@@ -31644,7 +31937,7 @@
           <t>Latin_America</t>
         </is>
       </c>
-      <c r="H101">
+      <c r="I101">
         <v>14050058.88347711</v>
       </c>
     </row>
@@ -31682,7 +31975,7 @@
           <t>Latin_America</t>
         </is>
       </c>
-      <c r="H102">
+      <c r="I102">
         <v>7623586.646322806</v>
       </c>
     </row>
@@ -31720,7 +32013,7 @@
           <t>Latin_America</t>
         </is>
       </c>
-      <c r="H103">
+      <c r="I103">
         <v>6761083.388006915</v>
       </c>
     </row>
@@ -31736,7 +32029,7 @@
         </is>
       </c>
       <c r="C104">
-        <v>9.569699999999999</v>
+        <v>10.0142</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -31758,8 +32051,8 @@
           <t>Latin_America</t>
         </is>
       </c>
-      <c r="H104">
-        <v>130230378.3012547</v>
+      <c r="I104">
+        <v>124450572.1777957</v>
       </c>
     </row>
     <row r="105">
@@ -31796,7 +32089,7 @@
           <t>Latin_America</t>
         </is>
       </c>
-      <c r="H105">
+      <c r="I105">
         <v>10652492.05314973</v>
       </c>
     </row>
@@ -32169,7 +32462,7 @@
         </is>
       </c>
       <c r="F9">
-        <v>130230378.3012547</v>
+        <v>124450572.1777957</v>
       </c>
       <c r="G9">
         <v>5717079</v>
@@ -32497,7 +32790,7 @@
         </is>
       </c>
       <c r="F17">
-        <v>130230378.3012547</v>
+        <v>124450572.1777957</v>
       </c>
       <c r="G17">
         <v>5717079</v>
@@ -32825,7 +33118,7 @@
         </is>
       </c>
       <c r="F25">
-        <v>130230378.3012547</v>
+        <v>124450572.1777957</v>
       </c>
       <c r="G25">
         <v>5717079</v>
@@ -33153,7 +33446,7 @@
         </is>
       </c>
       <c r="F33">
-        <v>125316843.1560066</v>
+        <v>120585765.7866152</v>
       </c>
       <c r="G33">
         <v>5717079</v>
@@ -33481,7 +33774,7 @@
         </is>
       </c>
       <c r="F41">
-        <v>125316843.1560066</v>
+        <v>120585765.7866152</v>
       </c>
       <c r="G41">
         <v>5717079</v>
@@ -33809,7 +34102,7 @@
         </is>
       </c>
       <c r="F49">
-        <v>125316843.1560066</v>
+        <v>120585765.7866152</v>
       </c>
       <c r="G49">
         <v>5717079</v>
@@ -34137,7 +34430,7 @@
         </is>
       </c>
       <c r="F57">
-        <v>135156546.2246397</v>
+        <v>128134171.3047735</v>
       </c>
       <c r="G57">
         <v>5717079</v>
@@ -34465,7 +34758,7 @@
         </is>
       </c>
       <c r="F65">
-        <v>135156546.2246397</v>
+        <v>128134171.3047735</v>
       </c>
       <c r="G65">
         <v>5717079</v>
@@ -34793,7 +35086,7 @@
         </is>
       </c>
       <c r="F73">
-        <v>135156546.2246397</v>
+        <v>128134171.3047735</v>
       </c>
       <c r="G73">
         <v>5717079</v>
@@ -35121,7 +35414,7 @@
         </is>
       </c>
       <c r="F81">
-        <v>129395956.970525</v>
+        <v>123815349.0395738</v>
       </c>
       <c r="G81">
         <v>5717079</v>
@@ -35449,7 +35742,7 @@
         </is>
       </c>
       <c r="F89">
-        <v>129395956.970525</v>
+        <v>123815349.0395738</v>
       </c>
       <c r="G89">
         <v>5717079</v>
@@ -35777,7 +36070,7 @@
         </is>
       </c>
       <c r="F97">
-        <v>129395956.970525</v>
+        <v>123815349.0395738</v>
       </c>
       <c r="G97">
         <v>5717079</v>
@@ -36064,7 +36357,7 @@
         </is>
       </c>
       <c r="F104">
-        <v>130230378.3012547</v>
+        <v>124450572.1777957</v>
       </c>
       <c r="G104">
         <v>5717079</v>
@@ -36500,10 +36793,10 @@
         </is>
       </c>
       <c r="H9">
-        <v>130230378.3012547</v>
+        <v>124450572.1777957</v>
       </c>
       <c r="I9">
-        <v>14525379.83735874</v>
+        <v>14106553.3066733</v>
       </c>
     </row>
     <row r="10">
@@ -36828,10 +37121,10 @@
         </is>
       </c>
       <c r="H17">
-        <v>130230378.3012547</v>
+        <v>124450572.1777957</v>
       </c>
       <c r="I17">
-        <v>14525379.83735874</v>
+        <v>14106553.3066733</v>
       </c>
     </row>
     <row r="18">
@@ -37156,10 +37449,10 @@
         </is>
       </c>
       <c r="H25">
-        <v>130230378.3012547</v>
+        <v>124450572.1777957</v>
       </c>
       <c r="I25">
-        <v>14525379.83735874</v>
+        <v>14106553.3066733</v>
       </c>
     </row>
     <row r="26">
@@ -37484,10 +37777,10 @@
         </is>
       </c>
       <c r="H33">
-        <v>125316843.1560066</v>
+        <v>120585765.7866152</v>
       </c>
       <c r="I33">
-        <v>14501129.6136672</v>
+        <v>14158297.92023304</v>
       </c>
     </row>
     <row r="34">
@@ -37812,10 +38105,10 @@
         </is>
       </c>
       <c r="H41">
-        <v>125316843.1560066</v>
+        <v>120585765.7866152</v>
       </c>
       <c r="I41">
-        <v>14501129.6136672</v>
+        <v>14158297.92023304</v>
       </c>
     </row>
     <row r="42">
@@ -38140,10 +38433,10 @@
         </is>
       </c>
       <c r="H49">
-        <v>125316843.1560066</v>
+        <v>120585765.7866152</v>
       </c>
       <c r="I49">
-        <v>14501129.6136672</v>
+        <v>14158297.92023304</v>
       </c>
     </row>
     <row r="50">
@@ -38468,10 +38761,10 @@
         </is>
       </c>
       <c r="H57">
-        <v>135156546.2246397</v>
+        <v>128134171.3047735</v>
       </c>
       <c r="I57">
-        <v>14471940.07208357</v>
+        <v>13963072.32426717</v>
       </c>
     </row>
     <row r="58">
@@ -38796,10 +39089,10 @@
         </is>
       </c>
       <c r="H65">
-        <v>135156546.2246397</v>
+        <v>128134171.3047735</v>
       </c>
       <c r="I65">
-        <v>14471940.07208357</v>
+        <v>13963072.32426717</v>
       </c>
     </row>
     <row r="66">
@@ -39124,10 +39417,10 @@
         </is>
       </c>
       <c r="H73">
-        <v>135156546.2246397</v>
+        <v>128134171.3047735</v>
       </c>
       <c r="I73">
-        <v>14471940.07208357</v>
+        <v>13963072.32426717</v>
       </c>
     </row>
     <row r="74">
@@ -39452,10 +39745,10 @@
         </is>
       </c>
       <c r="H81">
-        <v>129395956.970525</v>
+        <v>123815349.0395738</v>
       </c>
       <c r="I81">
-        <v>14456263.56642994</v>
+        <v>14051871.6873755</v>
       </c>
     </row>
     <row r="82">
@@ -39780,10 +40073,10 @@
         </is>
       </c>
       <c r="H89">
-        <v>129395956.970525</v>
+        <v>123815349.0395738</v>
       </c>
       <c r="I89">
-        <v>14456263.56642994</v>
+        <v>14051871.6873755</v>
       </c>
     </row>
     <row r="90">
@@ -40108,10 +40401,10 @@
         </is>
       </c>
       <c r="H97">
-        <v>129395956.970525</v>
+        <v>123815349.0395738</v>
       </c>
       <c r="I97">
-        <v>14456263.56642994</v>
+        <v>14051871.6873755</v>
       </c>
     </row>
     <row r="98">
@@ -40372,7 +40665,7 @@
         </is>
       </c>
       <c r="C104">
-        <v>8.5799</v>
+        <v>8.8347</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -40395,10 +40688,10 @@
         </is>
       </c>
       <c r="H104">
-        <v>130230378.3012547</v>
+        <v>124450572.1777957</v>
       </c>
       <c r="I104">
-        <v>14525379.83735874</v>
+        <v>14106553.3066733</v>
       </c>
     </row>
     <row r="105">
@@ -40806,7 +41099,7 @@
         </is>
       </c>
       <c r="C18">
-        <v>23395622.91577865</v>
+        <v>17615816.79231965</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -40826,7 +41119,7 @@
         </is>
       </c>
       <c r="C19">
-        <v>19150556.22201627</v>
+        <v>14419478.85262487</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -40846,7 +41139,7 @@
         </is>
       </c>
       <c r="C20">
-        <v>28425319.48114712</v>
+        <v>21402944.56128085</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -40866,7 +41159,7 @@
         </is>
       </c>
       <c r="C21">
-        <v>22589304.20925624</v>
+        <v>17008696.27830506</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -41526,7 +41819,7 @@
         </is>
       </c>
       <c r="C54">
-        <v>130230378.3012547</v>
+        <v>124450572.1777957</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -41546,7 +41839,7 @@
         </is>
       </c>
       <c r="C55">
-        <v>125316843.1560066</v>
+        <v>120585765.7866152</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -41566,7 +41859,7 @@
         </is>
       </c>
       <c r="C56">
-        <v>135156546.2246397</v>
+        <v>128134171.3047735</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -41586,7 +41879,7 @@
         </is>
       </c>
       <c r="C57">
-        <v>129395956.970525</v>
+        <v>123815349.0395738</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
